--- a/outputs/marine_equipment/Изменение_цен_по_ставке.xlsx
+++ b/outputs/marine_equipment/Изменение_цен_по_ставке.xlsx
@@ -627,16 +627,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>921</v>
+        <v>23</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1586</v>
+        <v>110</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>-3137241</v>
+        <v>-165866</v>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
@@ -651,16 +651,16 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>285</v>
+        <v>211</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>12521</v>
+        <v>11193</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>8754323</v>
+        <v>7883206</v>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
@@ -695,16 +695,16 @@
         </is>
       </c>
       <c r="B8" s="20" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="C8" s="20" t="n">
-        <v>1206</v>
+        <v>234</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>14107</v>
+        <v>11302</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>5617082</v>
+        <v>7717340</v>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>308</v>
+        <v>206</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>3738</v>
+        <v>3018</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>6962042</v>
+        <v>5621366</v>
       </c>
       <c r="F9" s="18" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -816,7 +816,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19 позиций  921 шт  1 586 кг. Итого -3 137 241 руб. Внутри группы — по размеру разницы на позицию.</t>
+          <t>6 позиций  23 шт  110 кг. Итого -165 866 руб. Внутри группы — по размеру разницы на позицию.</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>Штуцерная проходная — 2 позиции  -2 203 450 руб</t>
+          <t>Фланцевая угловая — 2 позиции  -136 584 руб</t>
         </is>
       </c>
     </row>
@@ -895,42 +895,42 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру40</t>
+          <t>Клапан фланцевый угловой Ду25</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>521-01.471-01</t>
+          <t>521-3М539</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>796</v>
+        <v>13</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>3000-5000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>2235</v>
+        <v>10244</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>-2765</v>
+        <v>-9756</v>
       </c>
       <c r="K6" s="27" t="n">
-        <v>-0.553</v>
+        <v>-0.4878</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>-2200940</v>
+        <v>-126828</v>
       </c>
     </row>
     <row r="7">
@@ -939,48 +939,48 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
+          <t>Клапан фланцевый угловой Ду25</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>528-35.176</t>
+          <t>521-3М.123</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>1490</v>
+        <v>10244</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>-2510</v>
+        <v>-9756</v>
       </c>
       <c r="K7" s="27" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.4878</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>-2510</v>
+        <v>-9756</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>Штуцерная  угол или проход не указан — 8 позиций  -409 441 руб</t>
+          <t>Краны — 1 позиция  -16 590 руб</t>
         </is>
       </c>
     </row>
@@ -990,787 +990,194 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
+          <t>Кран двухходовой штуцерный Ду20 Ру16</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>521-03.442-03</t>
+          <t>536-3М5</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>15-20</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>10244</v>
+        <v>2235</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>-9756</v>
+        <v>-2765</v>
       </c>
       <c r="K9" s="27" t="n">
-        <v>-0.4878</v>
+        <v>-0.553</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>-97560</v>
+        <v>-16590</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Клапан запорн.с присоед.под дюрит прох. Ду65</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>ИШТЛ.491112-003.04</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>30000</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>10616</v>
-      </c>
-      <c r="J10" s="7" t="n">
-        <v>-19384</v>
-      </c>
-      <c r="K10" s="27" t="n">
-        <v>-0.6461333333333333</v>
-      </c>
-      <c r="L10" s="7" t="n">
-        <v>-96920</v>
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>Захлопки — 1 позиция  -5 444 руб</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Клапан запорн.с присоед.под дюрит прох. Ду65</t>
+          <t>Захлопка фланцевая вертикальная Ду50</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>521-03.442-04</t>
+          <t>529-35.1400-01</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>10616</v>
+        <v>19556</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>-19384</v>
+        <v>-5444</v>
       </c>
       <c r="K11" s="27" t="n">
-        <v>-0.6461333333333333</v>
+        <v>-0.21776</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>-96920</v>
+        <v>-5444</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>ИШТЛ.491912-002.04</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>15-20</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>10244</v>
-      </c>
-      <c r="J12" s="7" t="n">
-        <v>-9756</v>
-      </c>
-      <c r="K12" s="27" t="n">
-        <v>-0.4878</v>
-      </c>
-      <c r="L12" s="7" t="n">
-        <v>-48780</v>
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>Педальные клапаны — 1 позиция  -4 756 руб</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
+          <t>Клапан педальный Ду25</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>ИШТЛ.491112-003.03</t>
+          <t>М528-03.001</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>5.5</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>15-20</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="H13" s="7" t="n">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>10244</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>-9756</v>
+        <v>-4756</v>
       </c>
       <c r="K13" s="27" t="n">
-        <v>-0.4878</v>
+        <v>-0.3170666666666667</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>-48780</v>
+        <v>-4756</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>522-03.124-04</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I14" s="7" t="n">
-        <v>2794</v>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>-17206</v>
-      </c>
-      <c r="K14" s="27" t="n">
-        <v>-0.8603</v>
-      </c>
-      <c r="L14" s="7" t="n">
-        <v>-17206</v>
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>Кингстоны — 1 позиция  -2 492 руб</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру1,3-6,5</t>
+          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>524-03.174</t>
+          <t>527-35.1165-01</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.8</v>
+        <v>9.4</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>3500</v>
+        <v>20000</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>1490</v>
+        <v>17508</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>-2010</v>
+        <v>-2492</v>
       </c>
       <c r="K15" s="27" t="n">
-        <v>-0.5742857142857143</v>
+        <v>-0.1246</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>-2010</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду10Ру2,5-6,5</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>524-03.173</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>3500</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>2235</v>
-      </c>
-      <c r="J16" s="7" t="n">
-        <v>-1265</v>
-      </c>
-      <c r="K16" s="27" t="n">
-        <v>-0.3614285714285714</v>
-      </c>
-      <c r="L16" s="7" t="n">
-        <v>-1265</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="26" t="inlineStr">
-        <is>
-          <t>Педальные клапаны — 2 позиции  -299 628 руб</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Клапан педальный Ду25</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>М528-03.001</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>10244</v>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>-4756</v>
-      </c>
-      <c r="K18" s="27" t="n">
-        <v>-0.3170666666666667</v>
-      </c>
-      <c r="L18" s="7" t="n">
-        <v>-294872</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Клапан педальный Ду25</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>М528-03.001</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>10244</v>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>-4756</v>
-      </c>
-      <c r="K19" s="27" t="n">
-        <v>-0.3170666666666667</v>
-      </c>
-      <c r="L19" s="7" t="n">
-        <v>-4756</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="26" t="inlineStr">
-        <is>
-          <t>Фланцевая угловая — 2 позиции  -136 584 руб</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Клапан фланцевый угловой Ду25</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>521-3М539</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>10244</v>
-      </c>
-      <c r="J21" s="7" t="n">
-        <v>-9756</v>
-      </c>
-      <c r="K21" s="27" t="n">
-        <v>-0.4878</v>
-      </c>
-      <c r="L21" s="7" t="n">
-        <v>-126828</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Клапан фланцевый угловой Ду25</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>521-3М.123</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>10244</v>
-      </c>
-      <c r="J22" s="7" t="n">
-        <v>-9756</v>
-      </c>
-      <c r="K22" s="27" t="n">
-        <v>-0.4878</v>
-      </c>
-      <c r="L22" s="7" t="n">
-        <v>-9756</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="26" t="inlineStr">
-        <is>
-          <t>Штуцерная угловая — 2 позиции  -63 612 руб</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Клапан угловой с присоединением под дюрит Ду50Ру4</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>521-03.445-04</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>2421</v>
-      </c>
-      <c r="J24" s="7" t="n">
-        <v>-12579</v>
-      </c>
-      <c r="K24" s="27" t="n">
-        <v>-0.8386</v>
-      </c>
-      <c r="L24" s="7" t="n">
-        <v>-50316</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Клапан невозв-запор.цапковый угловой  под дюрит Ду20Ру6</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>522-03.123</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I25" s="7" t="n">
-        <v>3352</v>
-      </c>
-      <c r="J25" s="7" t="n">
-        <v>-6648</v>
-      </c>
-      <c r="K25" s="27" t="n">
-        <v>-0.6647999999999999</v>
-      </c>
-      <c r="L25" s="7" t="n">
-        <v>-13296</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="26" t="inlineStr">
-        <is>
-          <t>Краны — 1 позиция  -16 590 руб</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Кран двухходовой штуцерный Ду20 Ру16</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>536-3М5</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I27" s="7" t="n">
-        <v>2235</v>
-      </c>
-      <c r="J27" s="7" t="n">
-        <v>-2765</v>
-      </c>
-      <c r="K27" s="27" t="n">
-        <v>-0.553</v>
-      </c>
-      <c r="L27" s="7" t="n">
-        <v>-16590</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="26" t="inlineStr">
-        <is>
-          <t>Захлопки — 1 позиция  -5 444 руб</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Захлопка фланцевая вертикальная Ду50</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>529-35.1400-01</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>25000</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I29" s="7" t="n">
-        <v>19556</v>
-      </c>
-      <c r="J29" s="7" t="n">
-        <v>-5444</v>
-      </c>
-      <c r="K29" s="27" t="n">
-        <v>-0.21776</v>
-      </c>
-      <c r="L29" s="7" t="n">
-        <v>-5444</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="26" t="inlineStr">
-        <is>
-          <t>Кингстоны — 1 позиция  -2 492 руб</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>527-35.1165-01</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>17508</v>
-      </c>
-      <c r="J31" s="7" t="n">
-        <v>-2492</v>
-      </c>
-      <c r="K31" s="27" t="n">
-        <v>-0.1246</v>
-      </c>
-      <c r="L31" s="7" t="n">
         <v>-2492</v>
       </c>
     </row>
@@ -1786,7 +1193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1813,7 +1220,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>63 позиции  285 шт  12 521 кг. Итого +8 754 323 руб. Внутри группы — по размеру разницы на позицию.</t>
+          <t>54 позиции  211 шт  11 193 кг. Итого +7 883 206 руб. Внутри группы — по размеру разницы на позицию.</t>
         </is>
       </c>
     </row>
@@ -2512,7 +1919,7 @@
     <row r="21">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>Фланцевая проходная — 19 позиций  +1 236 079 руб</t>
+          <t>Фильтры забортной воды — 3 позиции  +1 011 873 руб</t>
         </is>
       </c>
     </row>
@@ -2522,42 +1929,42 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50</t>
+          <t>Фильтр забортной воды Ду200</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>521-35.3442</t>
+          <t>427-03.112-2</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>17.8</v>
+        <v>148.5</v>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>15-20000</t>
+          <t>150-170</t>
         </is>
       </c>
       <c r="H22" s="12" t="n">
-        <v>20000</v>
+        <v>170000</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>33152</v>
+        <v>276581</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>13152</v>
+        <v>106581</v>
       </c>
       <c r="K22" s="28" t="n">
-        <v>0.6576</v>
+        <v>0.6269470588235294</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>789120</v>
+        <v>852648</v>
       </c>
     </row>
     <row r="23">
@@ -2566,42 +1973,42 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125</t>
+          <t>Фильтр заборной воды ДУ 150</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>521-03.491</t>
+          <t>427-30.240</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>45.5</v>
+        <v>64</v>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>55000</t>
+          <t>75-90</t>
         </is>
       </c>
       <c r="H23" s="12" t="n">
-        <v>55000</v>
+        <v>90000</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>84744</v>
+        <v>119200</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>29744</v>
+        <v>29200</v>
       </c>
       <c r="K23" s="28" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.3244444444444444</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>208208</v>
+        <v>146000</v>
       </c>
     </row>
     <row r="24">
@@ -2610,135 +2017,98 @@
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50</t>
+          <t>Фильтр забортной воды Ду 100</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>521-03.495</t>
+          <t>427-03.192-2</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>15-20000</t>
+          <t>55 000 - 65 000</t>
         </is>
       </c>
       <c r="H24" s="12" t="n">
-        <v>20000</v>
+        <v>65000</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>26075</v>
+        <v>78225</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>6075</v>
+        <v>13225</v>
       </c>
       <c r="K24" s="28" t="n">
-        <v>0.30375</v>
+        <v>0.2034615384615385</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>78975</v>
+        <v>13225</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>Клапан фланцевый проходной Ду125</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>521-35.3455-02</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>125</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <v>46</v>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>55000</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>55000</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>85675</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>30675</v>
-      </c>
-      <c r="K25" s="28" t="n">
-        <v>0.5577272727272727</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>61350</v>
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>Фланцевая проходная — 18 позиций  +446 959 руб</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50</t>
+          <t>Клапан фланцевый проходной Ду125</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>521-35.3442-01</t>
+          <t>521-03.491</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>19</v>
+        <v>45.5</v>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>15-20000</t>
+          <t>55000</t>
         </is>
       </c>
       <c r="H26" s="12" t="n">
-        <v>20000</v>
+        <v>55000</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>35388</v>
+        <v>84744</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>15388</v>
+        <v>29744</v>
       </c>
       <c r="K26" s="28" t="n">
-        <v>0.7694</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>15388</v>
+        <v>208208</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
@@ -2747,17 +2117,17 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>522-03.192</t>
+          <t>521-03.495</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
         <v>50</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
@@ -2768,65 +2138,65 @@
         <v>20000</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>25889</v>
+        <v>26075</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>5889</v>
+        <v>6075</v>
       </c>
       <c r="K27" s="28" t="n">
-        <v>0.29445</v>
+        <v>0.30375</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>11778</v>
+        <v>78975</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50</t>
+          <t>Клапан фланцевый проходной Ду125</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>УН522-3М97</t>
+          <t>521-35.3455-02</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>15-20000</t>
+          <t>55000</t>
         </is>
       </c>
       <c r="H28" s="12" t="n">
-        <v>20000</v>
+        <v>55000</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>22350</v>
+        <v>85675</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>2350</v>
+        <v>30675</v>
       </c>
       <c r="K28" s="28" t="n">
-        <v>0.1175</v>
+        <v>0.5577272727272727</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>11750</v>
+        <v>61350</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
@@ -2835,17 +2205,17 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>521-01.128</t>
+          <t>521-35.3442-01</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
         <v>50</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F29" s="10" t="n">
-        <v>11.9</v>
+        <v>19</v>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
@@ -2856,21 +2226,21 @@
         <v>20000</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>22164</v>
+        <v>35388</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>2164</v>
+        <v>15388</v>
       </c>
       <c r="K29" s="28" t="n">
-        <v>0.1082</v>
+        <v>0.7694</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>10820</v>
+        <v>15388</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
@@ -2879,17 +2249,17 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>521-01.182</t>
+          <t>522-03.192</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
         <v>50</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>11.3</v>
+        <v>13.9</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -2900,21 +2270,21 @@
         <v>20000</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>21046</v>
+        <v>25889</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>1046</v>
+        <v>5889</v>
       </c>
       <c r="K30" s="28" t="n">
-        <v>0.0523</v>
+        <v>0.29445</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>9414</v>
+        <v>11778</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
@@ -2923,14 +2293,14 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>522-35.4151-02</t>
+          <t>УН522-3М97</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
         <v>50</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F31" s="10" t="n">
         <v>12</v>
@@ -2953,12 +2323,12 @@
         <v>0.1175</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>7050</v>
+        <v>11750</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
@@ -2967,17 +2337,17 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>фланцы  брак</t>
+          <t>521-01.128</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
         <v>50</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -2988,21 +2358,21 @@
         <v>20000</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>22350</v>
+        <v>22164</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>2350</v>
+        <v>2164</v>
       </c>
       <c r="K32" s="28" t="n">
-        <v>0.1175</v>
+        <v>0.1082</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>7050</v>
+        <v>10820</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
@@ -3011,17 +2381,17 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>521-01.182</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
         <v>50</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>12</v>
+        <v>11.3</v>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
@@ -3032,21 +2402,21 @@
         <v>20000</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>22350</v>
+        <v>21046</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>2350</v>
+        <v>1046</v>
       </c>
       <c r="K33" s="28" t="n">
-        <v>0.1175</v>
+        <v>0.0523</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>7050</v>
+        <v>9414</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
@@ -3055,17 +2425,17 @@
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>521-35.3381</t>
+          <t>522-35.4151-02</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
         <v>50</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
@@ -3076,21 +2446,21 @@
         <v>20000</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>23281</v>
+        <v>22350</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>3281</v>
+        <v>2350</v>
       </c>
       <c r="K34" s="28" t="n">
-        <v>0.16405</v>
+        <v>0.1175</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>3281</v>
+        <v>7050</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
@@ -3099,17 +2469,17 @@
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>522-35.4076</t>
+          <t>фланцы  брак</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
         <v>50</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" s="10" t="n">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
@@ -3120,21 +2490,21 @@
         <v>20000</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>23095</v>
+        <v>22350</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>3095</v>
+        <v>2350</v>
       </c>
       <c r="K35" s="28" t="n">
-        <v>0.15475</v>
+        <v>0.1175</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>3095</v>
+        <v>7050</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
@@ -3143,14 +2513,14 @@
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>УН522-3М520</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
         <v>50</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" s="10" t="n">
         <v>12</v>
@@ -3173,12 +2543,12 @@
         <v>0.1175</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>2350</v>
+        <v>7050</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
@@ -3187,7 +2557,7 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>522-35.859</t>
+          <t>521-35.3381</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
@@ -3197,7 +2567,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
@@ -3208,21 +2578,21 @@
         <v>20000</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>22350</v>
+        <v>23281</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>2350</v>
+        <v>3281</v>
       </c>
       <c r="K37" s="28" t="n">
-        <v>0.1175</v>
+        <v>0.16405</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>2350</v>
+        <v>3281</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
@@ -3231,7 +2601,7 @@
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>522-01.174</t>
+          <t>522-35.4076</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
@@ -3241,7 +2611,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
@@ -3252,21 +2622,21 @@
         <v>20000</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>22350</v>
+        <v>23095</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>2350</v>
+        <v>3095</v>
       </c>
       <c r="K38" s="28" t="n">
-        <v>0.1175</v>
+        <v>0.15475</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>2350</v>
+        <v>3095</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
@@ -3275,7 +2645,7 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>522-3М.566</t>
+          <t>УН522-3М520</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
@@ -3310,7 +2680,7 @@
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
@@ -3319,7 +2689,7 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>522-01.224</t>
+          <t>522-35.859</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
@@ -3353,10 +2723,47 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="26" t="inlineStr">
-        <is>
-          <t>Фильтры забортной воды — 3 позиции  +1 011 873 руб</t>
-        </is>
+      <c r="A41" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной Ду50</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>522-01.174</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>15-20000</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>22350</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>2350</v>
+      </c>
+      <c r="K41" s="28" t="n">
+        <v>0.1175</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>2350</v>
       </c>
     </row>
     <row r="42">
@@ -3365,42 +2772,42 @@
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду200</t>
+          <t>Клапан фланцевый проходной Ду50</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>427-03.112-2</t>
+          <t>522-3М.566</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>148.5</v>
+        <v>12</v>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>150-170</t>
+          <t>15-20000</t>
         </is>
       </c>
       <c r="H42" s="12" t="n">
-        <v>170000</v>
+        <v>20000</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>276581</v>
+        <v>22350</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>106581</v>
+        <v>2350</v>
       </c>
       <c r="K42" s="28" t="n">
-        <v>0.6269470588235294</v>
+        <v>0.1175</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>852648</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="43">
@@ -3409,93 +2816,93 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>Фильтр заборной воды ДУ 150</t>
+          <t>Клапан фланцевый проходной Ду50</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>427-30.240</t>
+          <t>522-01.224</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>75-90</t>
+          <t>15-20000</t>
         </is>
       </c>
       <c r="H43" s="12" t="n">
-        <v>90000</v>
+        <v>20000</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>119200</v>
+        <v>22350</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>29200</v>
+        <v>2350</v>
       </c>
       <c r="K43" s="28" t="n">
-        <v>0.3244444444444444</v>
+        <v>0.1175</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>146000</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="n">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>Фланцевая угловая — 11 позиций  +281 110 руб</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>Фильтр забортной воды Ду 100</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>427-03.192-2</t>
-        </is>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="G44" s="9" t="inlineStr">
-        <is>
-          <t>55 000 - 65 000</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="n">
-        <v>65000</v>
-      </c>
-      <c r="I44" s="12" t="n">
-        <v>78225</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>13225</v>
-      </c>
-      <c r="K44" s="28" t="n">
-        <v>0.2034615384615385</v>
-      </c>
-      <c r="L44" s="12" t="n">
-        <v>13225</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="26" t="inlineStr">
-        <is>
-          <t>Фланцевая угловая — 16 позиций  +349 341 руб</t>
-        </is>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду80</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>522-35.4170-02</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>48425</v>
+      </c>
+      <c r="J45" s="12" t="n">
+        <v>18425</v>
+      </c>
+      <c r="K45" s="28" t="n">
+        <v>0.6141666666666666</v>
+      </c>
+      <c r="L45" s="12" t="n">
+        <v>73700</v>
       </c>
     </row>
     <row r="46">
@@ -3504,22 +2911,22 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду80</t>
+          <t>Клапан фланцевый угловой Ду100</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>522-35.4170-02</t>
+          <t>522-03.197</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
@@ -3530,16 +2937,16 @@
         <v>30000</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>48425</v>
+        <v>52150</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>18425</v>
+        <v>22150</v>
       </c>
       <c r="K46" s="28" t="n">
-        <v>0.6141666666666666</v>
+        <v>0.7383333333333333</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>73700</v>
+        <v>44300</v>
       </c>
     </row>
     <row r="47">
@@ -3548,22 +2955,22 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду100</t>
+          <t>Клапан фланцевый угловой Ду80</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>522-03.197</t>
+          <t>522-03.196</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
@@ -3574,16 +2981,16 @@
         <v>30000</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>52150</v>
+        <v>37250</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>22150</v>
+        <v>7250</v>
       </c>
       <c r="K47" s="28" t="n">
-        <v>0.7383333333333333</v>
+        <v>0.2416666666666667</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>44300</v>
+        <v>36250</v>
       </c>
     </row>
     <row r="48">
@@ -3597,17 +3004,17 @@
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>522-03.196</t>
+          <t>522-01.194</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
         <v>80</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
@@ -3618,16 +3025,16 @@
         <v>30000</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>37250</v>
+        <v>36319</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>7250</v>
+        <v>6319</v>
       </c>
       <c r="K48" s="28" t="n">
-        <v>0.2416666666666667</v>
+        <v>0.2106333333333333</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>36250</v>
+        <v>25276</v>
       </c>
     </row>
     <row r="49">
@@ -3641,17 +3048,17 @@
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>522-03.196</t>
+          <t>521-35.3389</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
         <v>80</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
@@ -3662,16 +3069,16 @@
         <v>30000</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>37250</v>
+        <v>41906</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>7250</v>
+        <v>11906</v>
       </c>
       <c r="K49" s="28" t="n">
-        <v>0.2416666666666667</v>
+        <v>0.3968666666666666</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>29000</v>
+        <v>23812</v>
       </c>
     </row>
     <row r="50">
@@ -3685,17 +3092,17 @@
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>522-01.194</t>
+          <t>521-35.3453-02</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
         <v>80</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
@@ -3706,16 +3113,16 @@
         <v>30000</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>36319</v>
+        <v>37250</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>6319</v>
+        <v>7250</v>
       </c>
       <c r="K50" s="28" t="n">
-        <v>0.2106333333333333</v>
+        <v>0.2416666666666667</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>25276</v>
+        <v>21750</v>
       </c>
     </row>
     <row r="51">
@@ -3729,17 +3136,17 @@
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>521-35.3389</t>
+          <t>522-35.4074</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
         <v>80</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>22.5</v>
+        <v>24.5</v>
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
@@ -3750,16 +3157,16 @@
         <v>30000</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>41906</v>
+        <v>45631</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>11906</v>
+        <v>15631</v>
       </c>
       <c r="K51" s="28" t="n">
-        <v>0.3968666666666666</v>
+        <v>0.5210333333333333</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>23812</v>
+        <v>15631</v>
       </c>
     </row>
     <row r="52">
@@ -3773,14 +3180,14 @@
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>521-35.3453-02</t>
+          <t>522-01.244</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
         <v>80</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F52" s="10" t="n">
         <v>20</v>
@@ -3803,7 +3210,7 @@
         <v>0.2416666666666667</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>21750</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="53">
@@ -3812,42 +3219,42 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду80</t>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>521-35.011</t>
+          <t>522-35.4154-02</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F53" s="10" t="n">
-        <v>25.5</v>
+        <v>16</v>
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="H53" s="12" t="n">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>47494</v>
+        <v>29800</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>17494</v>
+        <v>4800</v>
       </c>
       <c r="K53" s="28" t="n">
-        <v>0.5831333333333333</v>
+        <v>0.192</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>17494</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="54">
@@ -3856,42 +3263,42 @@
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду80</t>
+          <t>Клапан фланцевый угловой Ду65 Ру10</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>522-35.4074</t>
+          <t>522-35.4201</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E54" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>24.5</v>
+        <v>17</v>
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="H54" s="12" t="n">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>45631</v>
+        <v>31662</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>15631</v>
+        <v>6662</v>
       </c>
       <c r="K54" s="28" t="n">
-        <v>0.5210333333333333</v>
+        <v>0.26648</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>15631</v>
+        <v>6662</v>
       </c>
     </row>
     <row r="55">
@@ -3905,17 +3312,17 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>522-01.244</t>
+          <t>521-01.204</t>
         </is>
       </c>
       <c r="D55" s="10" t="n">
         <v>80</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>20</v>
+        <v>18.7</v>
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
@@ -3926,84 +3333,47 @@
         <v>30000</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>37250</v>
+        <v>34829</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>7250</v>
+        <v>4829</v>
       </c>
       <c r="K55" s="28" t="n">
-        <v>0.2416666666666667</v>
+        <v>0.1609666666666667</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>14500</v>
+        <v>4829</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="n">
-        <v>47</v>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>Клапан фланцевый угловой Ду65 Ру10</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>522-35.4154-02</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="n">
-        <v>65</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F56" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>25000</t>
-        </is>
-      </c>
-      <c r="H56" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I56" s="12" t="n">
-        <v>29800</v>
-      </c>
-      <c r="J56" s="12" t="n">
-        <v>4800</v>
-      </c>
-      <c r="K56" s="28" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="L56" s="12" t="n">
-        <v>14400</v>
+      <c r="A56" s="26" t="inlineStr">
+        <is>
+          <t>Кингстоны — 2 позиции  +8 226 руб</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду80</t>
+          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>521-01.150-02</t>
+          <t>527-35.1166-01</t>
         </is>
       </c>
       <c r="D57" s="10" t="n">
         <v>80</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>18.7</v>
+        <v>20</v>
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
@@ -4014,711 +3384,345 @@
         <v>30000</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>34829</v>
+        <v>37250</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>4829</v>
+        <v>7250</v>
       </c>
       <c r="K57" s="28" t="n">
-        <v>0.1609666666666667</v>
+        <v>0.2416666666666667</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>9658</v>
+        <v>7250</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду80</t>
+          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>522-01.244</t>
+          <t>527-03.054</t>
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="H58" s="12" t="n">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>37250</v>
+        <v>20488</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>7250</v>
+        <v>488</v>
       </c>
       <c r="K58" s="28" t="n">
-        <v>0.2416666666666667</v>
+        <v>0.0244</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>7250</v>
+        <v>976</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="B59" s="13" t="inlineStr">
-        <is>
-          <t>Клапан фланцевый угловой Ду65 Ру10</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>522-35.4201</t>
-        </is>
-      </c>
-      <c r="D59" s="10" t="n">
-        <v>65</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>25000</t>
-        </is>
-      </c>
-      <c r="H59" s="12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I59" s="12" t="n">
-        <v>31662</v>
-      </c>
-      <c r="J59" s="12" t="n">
-        <v>6662</v>
-      </c>
-      <c r="K59" s="28" t="n">
-        <v>0.26648</v>
-      </c>
-      <c r="L59" s="12" t="n">
-        <v>6662</v>
+      <c r="A59" s="26" t="inlineStr">
+        <is>
+          <t>Захлопки — 2 позиции  +7 855 руб</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду80</t>
+          <t>Захлопка фланцевая проходная Ду100</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>521-01.150</t>
+          <t>529-35.1406-01</t>
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E60" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>18.7</v>
+        <v>23.6</v>
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="H60" s="12" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>34829</v>
+        <v>43955</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>4829</v>
+        <v>3955</v>
       </c>
       <c r="K60" s="28" t="n">
-        <v>0.1609666666666667</v>
+        <v>0.098875</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>4829</v>
+        <v>3955</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду80</t>
+          <t>Захлопка фланцевая горизон. Ду100</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>521-01.204</t>
+          <t>529-03.074</t>
         </is>
       </c>
       <c r="D61" s="10" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>18.7</v>
+        <v>22</v>
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="H61" s="12" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>34829</v>
+        <v>40975</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>4829</v>
+        <v>975</v>
       </c>
       <c r="K61" s="28" t="n">
-        <v>0.1609666666666667</v>
+        <v>0.024375</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>4829</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="26" t="inlineStr">
         <is>
-          <t>Кингстоны — 3 позиции  +19 002 руб</t>
+          <t>Штуцерная угловая — 2 позиции  +4 301 руб</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
+          <t>Клапан штуцерный угловой Ду32</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>527-03.055</t>
+          <t>521-01.468-07</t>
         </is>
       </c>
       <c r="D63" s="10" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="E63" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>19</v>
+        <v>3.7</v>
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="H63" s="12" t="n">
-        <v>30000</v>
+        <v>6500</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>35388</v>
+        <v>6891</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>5388</v>
+        <v>391</v>
       </c>
       <c r="K63" s="28" t="n">
-        <v>0.1796</v>
+        <v>0.06015384615384615</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>10776</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
+          <t>Клапан штуцерный угловой Ду32,без маховика , без крышки корпуса</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>527-35.1166-01</t>
+          <t>522-01.500-07</t>
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64" s="10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>6500</t>
+        </is>
+      </c>
+      <c r="H64" s="12" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I64" s="12" t="n">
+        <v>6891</v>
+      </c>
+      <c r="J64" s="12" t="n">
+        <v>391</v>
+      </c>
+      <c r="K64" s="28" t="n">
+        <v>0.06015384615384615</v>
+      </c>
+      <c r="L64" s="12" t="n">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="26" t="inlineStr">
+        <is>
+          <t>Краны — 2 позиции  +2 641 руб</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="n">
+        <v>53</v>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>Кран трехходовой штуцерный Ду20 Ру16</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>536-35.695</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
-      </c>
-      <c r="H64" s="12" t="n">
-        <v>30000</v>
-      </c>
-      <c r="I64" s="12" t="n">
-        <v>37250</v>
-      </c>
-      <c r="J64" s="12" t="n">
-        <v>7250</v>
-      </c>
-      <c r="K64" s="28" t="n">
-        <v>0.2416666666666667</v>
-      </c>
-      <c r="L64" s="12" t="n">
-        <v>7250</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
-        </is>
-      </c>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>527-03.054</t>
-        </is>
-      </c>
-      <c r="D65" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F65" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
-      </c>
-      <c r="H65" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I65" s="12" t="n">
-        <v>20488</v>
-      </c>
-      <c r="J65" s="12" t="n">
-        <v>488</v>
-      </c>
-      <c r="K65" s="28" t="n">
-        <v>0.0244</v>
-      </c>
-      <c r="L65" s="12" t="n">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="26" t="inlineStr">
-        <is>
-          <t>Захлопки — 2 позиции  +7 855 руб</t>
-        </is>
+      <c r="E66" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F66" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="H66" s="12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I66" s="12" t="n">
+        <v>5215</v>
+      </c>
+      <c r="J66" s="12" t="n">
+        <v>215</v>
+      </c>
+      <c r="K66" s="28" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="L66" s="12" t="n">
+        <v>1505</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая проходная Ду100</t>
+          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>529-35.1406-01</t>
+          <t>536-35.696</t>
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="E67" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="10" t="n">
-        <v>23.6</v>
+        <v>4.1</v>
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="H67" s="12" t="n">
-        <v>40000</v>
+        <v>6500</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>43955</v>
+        <v>7636</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>3955</v>
+        <v>1136</v>
       </c>
       <c r="K67" s="28" t="n">
-        <v>0.098875</v>
+        <v>0.1747692307692308</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>3955</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="10" t="n">
-        <v>57</v>
-      </c>
-      <c r="B68" s="13" t="inlineStr">
-        <is>
-          <t>Захлопка фланцевая горизон. Ду100</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>529-03.074</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F68" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>40000</t>
-        </is>
-      </c>
-      <c r="H68" s="12" t="n">
-        <v>40000</v>
-      </c>
-      <c r="I68" s="12" t="n">
-        <v>40975</v>
-      </c>
-      <c r="J68" s="12" t="n">
-        <v>975</v>
-      </c>
-      <c r="K68" s="28" t="n">
-        <v>0.024375</v>
-      </c>
-      <c r="L68" s="12" t="n">
-        <v>3900</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="26" t="inlineStr">
-        <is>
-          <t>Краны — 3 позиции  +4 913 руб</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
-        <is>
-          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>536-35.696</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F70" s="10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
-          <t>6500</t>
-        </is>
-      </c>
-      <c r="H70" s="12" t="n">
-        <v>6500</v>
-      </c>
-      <c r="I70" s="12" t="n">
-        <v>7636</v>
-      </c>
-      <c r="J70" s="12" t="n">
         <v>1136</v>
-      </c>
-      <c r="K70" s="28" t="n">
-        <v>0.1747692307692308</v>
-      </c>
-      <c r="L70" s="12" t="n">
-        <v>2272</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="B71" s="13" t="inlineStr">
-        <is>
-          <t>Кран трехходовой штуцерный Ду20 Ру16</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>536-35.695</t>
-        </is>
-      </c>
-      <c r="D71" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F71" s="10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="H71" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I71" s="12" t="n">
-        <v>5215</v>
-      </c>
-      <c r="J71" s="12" t="n">
-        <v>215</v>
-      </c>
-      <c r="K71" s="28" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="L71" s="12" t="n">
-        <v>1505</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="B72" s="13" t="inlineStr">
-        <is>
-          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
-        </is>
-      </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>536-35.696</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>6500</t>
-        </is>
-      </c>
-      <c r="H72" s="12" t="n">
-        <v>6500</v>
-      </c>
-      <c r="I72" s="12" t="n">
-        <v>7636</v>
-      </c>
-      <c r="J72" s="12" t="n">
-        <v>1136</v>
-      </c>
-      <c r="K72" s="28" t="n">
-        <v>0.1747692307692308</v>
-      </c>
-      <c r="L72" s="12" t="n">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="26" t="inlineStr">
-        <is>
-          <t>Штуцерная угловая — 2 позиции  +4 301 руб</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="10" t="n">
-        <v>61</v>
-      </c>
-      <c r="B74" s="13" t="inlineStr">
-        <is>
-          <t>Клапан штуцерный угловой Ду32</t>
-        </is>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>521-01.468-07</t>
-        </is>
-      </c>
-      <c r="D74" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F74" s="10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="G74" s="9" t="inlineStr">
-        <is>
-          <t>6500</t>
-        </is>
-      </c>
-      <c r="H74" s="12" t="n">
-        <v>6500</v>
-      </c>
-      <c r="I74" s="12" t="n">
-        <v>6891</v>
-      </c>
-      <c r="J74" s="12" t="n">
-        <v>391</v>
-      </c>
-      <c r="K74" s="28" t="n">
-        <v>0.06015384615384615</v>
-      </c>
-      <c r="L74" s="12" t="n">
-        <v>3128</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="n">
-        <v>62</v>
-      </c>
-      <c r="B75" s="13" t="inlineStr">
-        <is>
-          <t>Клапан штуцерный угловой Ду32,без маховика , без крышки корпуса</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>522-01.500-07</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F75" s="10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>6500</t>
-        </is>
-      </c>
-      <c r="H75" s="12" t="n">
-        <v>6500</v>
-      </c>
-      <c r="I75" s="12" t="n">
-        <v>6891</v>
-      </c>
-      <c r="J75" s="12" t="n">
-        <v>391</v>
-      </c>
-      <c r="K75" s="28" t="n">
-        <v>0.06015384615384615</v>
-      </c>
-      <c r="L75" s="12" t="n">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="26" t="inlineStr">
-        <is>
-          <t>Паровые клапаны — 1 позиция  +718 руб</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="n">
-        <v>63</v>
-      </c>
-      <c r="B77" s="13" t="inlineStr">
-        <is>
-          <t>Клапан паровой Ду65Ру10</t>
-        </is>
-      </c>
-      <c r="C77" s="9" t="inlineStr">
-        <is>
-          <t>581-03.034</t>
-        </is>
-      </c>
-      <c r="D77" s="10" t="n">
-        <v>65</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" s="10" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>50-60</t>
-        </is>
-      </c>
-      <c r="H77" s="12" t="n">
-        <v>60000</v>
-      </c>
-      <c r="I77" s="12" t="n">
-        <v>60718</v>
-      </c>
-      <c r="J77" s="12" t="n">
-        <v>718</v>
-      </c>
-      <c r="K77" s="28" t="n">
-        <v>0.01196666666666667</v>
-      </c>
-      <c r="L77" s="12" t="n">
-        <v>718</v>
       </c>
     </row>
   </sheetData>
@@ -4733,7 +3737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4756,7 +3760,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>80 позиций  308 шт  3 738 кг на 6 962 042 руб. В договоре их не было совсем или стояло «по согласованию» — сравнивать не с чем  это новая цена  а не изменение.</t>
+          <t>57 позиций  206 шт  3 018 кг на 5 621 366 руб. В договоре их не было совсем или стояло «по согласованию» — сравнивать не с чем  это новая цена  а не изменение.</t>
         </is>
       </c>
     </row>
@@ -4898,28 +3902,28 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду80</t>
+          <t>Задвижка клинкетная  Ду 250, без штока</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>(541-03.218)</t>
+          <t>532-01.022</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>11.2</v>
+        <v>100</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>20860</v>
+        <v>186250</v>
       </c>
       <c r="H8" s="17" t="n">
-        <v>396340</v>
+        <v>372500</v>
       </c>
     </row>
     <row r="9">
@@ -4928,28 +3932,28 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная  Ду 250, без штока</t>
+          <t>Задвижка клинкетная Ду 300 в разборе , шток отдельно</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>532-01.022</t>
+          <t>532-01.023</t>
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>100</v>
+        <v>192</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>186250</v>
+        <v>357600</v>
       </c>
       <c r="H9" s="17" t="n">
-        <v>372500</v>
+        <v>357600</v>
       </c>
     </row>
     <row r="10">
@@ -4958,28 +3962,28 @@
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 300 в разборе , шток отдельно</t>
+          <t>Клапан фланцевый угловой Ду100</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>532-01.023</t>
+          <t>522-01.245</t>
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>357600</v>
+        <v>52150</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>357600</v>
+        <v>312900</v>
       </c>
     </row>
     <row r="11">
@@ -4988,28 +3992,28 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду100</t>
+          <t>Клапан фланцевый проходной Ду200</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>522-01.245</t>
+          <t>522-01.232</t>
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>52150</v>
+        <v>204875</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>312900</v>
+        <v>204875</v>
       </c>
     </row>
     <row r="12">
@@ -5018,28 +4022,28 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>Клапан невозвратный Ду 100</t>
+          <t>Фильтр заборной воды ДУ 80</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>522-03.205</t>
+          <t>427-03.108-2</t>
         </is>
       </c>
       <c r="D12" s="15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E12" s="15" t="n">
         <v>4</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>28.8</v>
+        <v>27</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>53640</v>
+        <v>50288</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>214560</v>
+        <v>201152</v>
       </c>
     </row>
     <row r="13">
@@ -5048,28 +4052,28 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду200</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>522-01.232</t>
+          <t>522-01.501-02</t>
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>110</v>
+        <v>2.1</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>204875</v>
+        <v>3911</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>204875</v>
+        <v>175995</v>
       </c>
     </row>
     <row r="14">
@@ -5078,28 +4082,28 @@
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду125 (без поплавка)</t>
+          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду65Ру6,3</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>(541-03.220)</t>
+          <t>521-03.022</t>
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>18.2</v>
+        <v>22.5</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>33898</v>
+        <v>41906</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>203388</v>
+        <v>167624</v>
       </c>
     </row>
     <row r="15">
@@ -5108,28 +4112,28 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Фильтр заборной воды ДУ 80</t>
+          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду100</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>427-03.108-2</t>
+          <t>521-03.023</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>50288</v>
+        <v>67050</v>
       </c>
       <c r="H15" s="17" t="n">
-        <v>201152</v>
+        <v>134100</v>
       </c>
     </row>
     <row r="16">
@@ -5138,28 +4142,28 @@
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан фланцевый проходной Ду125</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>522-01.501-02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="F16" s="15" t="n">
-        <v>2.1</v>
+        <v>60</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>3911</v>
+        <v>111750</v>
       </c>
       <c r="H16" s="17" t="n">
-        <v>175995</v>
+        <v>111750</v>
       </c>
     </row>
     <row r="17">
@@ -5168,28 +4172,28 @@
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду65Ру6,3</t>
+          <t>Клапан фланцевый проходной Ду125</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>521-03.022</t>
+          <t>522-.....</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>22.5</v>
+        <v>46</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>41906</v>
+        <v>85675</v>
       </c>
       <c r="H17" s="17" t="n">
-        <v>167624</v>
+        <v>85675</v>
       </c>
     </row>
     <row r="18">
@@ -5198,28 +4202,28 @@
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду100</t>
+          <t>Задвижка клинкетная Ду 125</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>521-03.023</t>
+          <t>532-01.018</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>36</v>
+        <v>37.2</v>
       </c>
       <c r="G18" s="17" t="n">
-        <v>67050</v>
+        <v>69285</v>
       </c>
       <c r="H18" s="17" t="n">
-        <v>134100</v>
+        <v>69285</v>
       </c>
     </row>
     <row r="19">
@@ -5228,28 +4232,28 @@
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>Клапан невозвратно -приемный Ду 50</t>
+          <t>Клапан фланцевый угловой Ду100</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>522-35.4043-01</t>
+          <t>522-35.4206</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>10.8</v>
+        <v>35.4</v>
       </c>
       <c r="G19" s="17" t="n">
-        <v>20115</v>
+        <v>65932</v>
       </c>
       <c r="H19" s="17" t="n">
-        <v>120690</v>
+        <v>65932</v>
       </c>
     </row>
     <row r="20">
@@ -5258,28 +4262,28 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125</t>
+          <t>Захлопка фланцевая вертикальная Ду100</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>529-03.003</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E20" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>60</v>
+        <v>33.7</v>
       </c>
       <c r="G20" s="17" t="n">
-        <v>111750</v>
+        <v>62766</v>
       </c>
       <c r="H20" s="17" t="n">
-        <v>111750</v>
+        <v>62766</v>
       </c>
     </row>
     <row r="21">
@@ -5288,28 +4292,28 @@
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125</t>
+          <t>Клапан фланцевый проходной Ду100</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>522-.....</t>
+          <t>521-3М.511</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E21" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="G21" s="17" t="n">
-        <v>85675</v>
+        <v>54012</v>
       </c>
       <c r="H21" s="17" t="n">
-        <v>85675</v>
+        <v>54012</v>
       </c>
     </row>
     <row r="22">
@@ -5318,28 +4322,28 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду20Ру100</t>
+          <t>Задвижка клинкетная Ду 100</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>554-03.905-06</t>
+          <t>532-01.017</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>1.5</v>
+        <v>28.3</v>
       </c>
       <c r="G22" s="17" t="n">
-        <v>2794</v>
+        <v>52709</v>
       </c>
       <c r="H22" s="17" t="n">
-        <v>72644</v>
+        <v>52709</v>
       </c>
     </row>
     <row r="23">
@@ -5348,28 +4352,28 @@
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 125</t>
+          <t>Клапан фланцевый угловой Ду100</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>532-01.018</t>
+          <t>522-35.4171-02</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E23" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>37.2</v>
+        <v>28</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>69285</v>
+        <v>52150</v>
       </c>
       <c r="H23" s="17" t="n">
-        <v>69285</v>
+        <v>52150</v>
       </c>
     </row>
     <row r="24">
@@ -5378,28 +4382,28 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду100</t>
+          <t>Фильтр штуцрный Ду 25</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>522-35.4206</t>
+          <t>427-03.129-1</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>35.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G24" s="17" t="n">
-        <v>65932</v>
+        <v>17135</v>
       </c>
       <c r="H24" s="17" t="n">
-        <v>65932</v>
+        <v>51405</v>
       </c>
     </row>
     <row r="25">
@@ -5408,12 +4412,12 @@
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая вертикальная Ду100</t>
+          <t>Захлопка фланцевая угловая Ду100</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>529-03.003</t>
+          <t>529-35-1405</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
@@ -5423,13 +4427,13 @@
         <v>1</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>33.7</v>
+        <v>26</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>62766</v>
+        <v>48425</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>62766</v>
+        <v>48425</v>
       </c>
     </row>
     <row r="26">
@@ -5438,12 +4442,12 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду100</t>
+          <t>Захлопка фланцевая угловая Ду100</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>521-3М.511</t>
+          <t>529-03.073</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
@@ -5453,13 +4457,13 @@
         <v>1</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>29</v>
+        <v>24.7</v>
       </c>
       <c r="G26" s="17" t="n">
-        <v>54012</v>
+        <v>46004</v>
       </c>
       <c r="H26" s="17" t="n">
-        <v>54012</v>
+        <v>46004</v>
       </c>
     </row>
     <row r="27">
@@ -5468,28 +4472,28 @@
       </c>
       <c r="B27" s="18" t="inlineStr">
         <is>
-          <t>Клапан невозвратный Ду 100</t>
+          <t>Фильтр однопатронный фланцевый Ду 80</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>522-01.168</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E27" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>28.8</v>
+        <v>20</v>
       </c>
       <c r="G27" s="17" t="n">
-        <v>53640</v>
+        <v>37250</v>
       </c>
       <c r="H27" s="17" t="n">
-        <v>53640</v>
+        <v>37250</v>
       </c>
     </row>
     <row r="28">
@@ -5498,28 +4502,28 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 100</t>
+          <t>Кран трехходовой штуцерный Ду70</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>532-01.017</t>
+          <t>536-3м....</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E28" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>28.3</v>
+        <v>17.2</v>
       </c>
       <c r="G28" s="17" t="n">
-        <v>52709</v>
+        <v>32035</v>
       </c>
       <c r="H28" s="17" t="n">
-        <v>52709</v>
+        <v>32035</v>
       </c>
     </row>
     <row r="29">
@@ -5528,28 +4532,28 @@
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду100</t>
+          <t>Клапан фланцевый угловой Ду32 Ру25</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>522-35.4171-02</t>
+          <t>522-01.239</t>
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>28</v>
+        <v>5.6</v>
       </c>
       <c r="G29" s="17" t="n">
-        <v>52150</v>
+        <v>10430</v>
       </c>
       <c r="H29" s="17" t="n">
-        <v>52150</v>
+        <v>31290</v>
       </c>
     </row>
     <row r="30">
@@ -5558,28 +4562,28 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>Фильтр штуцрный Ду 25</t>
+          <t>Клапан фланцевый проходной ДУ20 Ру25</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>427-03.129-1</t>
+          <t>УН521-3М.324</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E30" s="15" t="n">
         <v>3</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>9.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="G30" s="17" t="n">
-        <v>17135</v>
+        <v>9871</v>
       </c>
       <c r="H30" s="17" t="n">
-        <v>51405</v>
+        <v>29613</v>
       </c>
     </row>
     <row r="31">
@@ -5588,28 +4592,28 @@
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 РУ 25</t>
+          <t>Клапан штуцерный угловой Ду25 Ру 40 без маховика , без крышки корпуса</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>522-35.446</t>
+          <t>521-01.466</t>
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>13.1</v>
+        <v>3.1</v>
       </c>
       <c r="G31" s="17" t="n">
-        <v>24399</v>
+        <v>5774</v>
       </c>
       <c r="H31" s="17" t="n">
-        <v>48798</v>
+        <v>28870</v>
       </c>
     </row>
     <row r="32">
@@ -5618,28 +4622,28 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая угловая Ду100</t>
+          <t>Клапан штуцерный угловой Ду25 Ру 40</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>529-35-1405</t>
+          <t>521-3м.634</t>
         </is>
       </c>
       <c r="D32" s="15" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>26</v>
+        <v>3.1</v>
       </c>
       <c r="G32" s="17" t="n">
-        <v>48425</v>
+        <v>5774</v>
       </c>
       <c r="H32" s="17" t="n">
-        <v>48425</v>
+        <v>28870</v>
       </c>
     </row>
     <row r="33">
@@ -5648,28 +4652,28 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая угловая Ду100</t>
+          <t>Клапан фланцевый угловой Ду70</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>529-03.073</t>
+          <t>522-3м.575</t>
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E33" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>24.7</v>
+        <v>15.5</v>
       </c>
       <c r="G33" s="17" t="n">
-        <v>46004</v>
+        <v>28869</v>
       </c>
       <c r="H33" s="17" t="n">
-        <v>46004</v>
+        <v>28869</v>
       </c>
     </row>
     <row r="34">
@@ -5678,7 +4682,7 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>Фильтр однопатронный фланцевый Ду 80</t>
+          <t>Кран трехходовой штуцерный Ду65 Ру10</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -5687,19 +4691,19 @@
         </is>
       </c>
       <c r="D34" s="15" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E34" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G34" s="17" t="n">
-        <v>37250</v>
+        <v>27938</v>
       </c>
       <c r="H34" s="17" t="n">
-        <v>37250</v>
+        <v>27938</v>
       </c>
     </row>
     <row r="35">
@@ -5708,28 +4712,28 @@
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду65 Ру40</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>521-03.230</t>
+          <t>521-3м.58</t>
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>20</v>
+        <v>2.1</v>
       </c>
       <c r="G35" s="17" t="n">
-        <v>37250</v>
+        <v>3911</v>
       </c>
       <c r="H35" s="17" t="n">
-        <v>37250</v>
+        <v>27377</v>
       </c>
     </row>
     <row r="36">
@@ -5738,28 +4742,28 @@
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>Кран трехходовой штуцерный Ду70</t>
+          <t>Захлопка фланцевая горизонтальная Ду80</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>536-3м....</t>
+          <t>529-03.071</t>
         </is>
       </c>
       <c r="D36" s="15" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E36" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>17.2</v>
+        <v>14.4</v>
       </c>
       <c r="G36" s="17" t="n">
-        <v>32035</v>
+        <v>26820</v>
       </c>
       <c r="H36" s="17" t="n">
-        <v>32035</v>
+        <v>26820</v>
       </c>
     </row>
     <row r="37">
@@ -5768,28 +4772,28 @@
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной бессальниковый  Ду15/1</t>
+          <t>Задвижка клинкетная Ду60</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>521-35.2608-01</t>
+          <t>532-01.014</t>
         </is>
       </c>
       <c r="D37" s="15" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>5.7</v>
+        <v>12.2</v>
       </c>
       <c r="G37" s="17" t="n">
-        <v>10616</v>
+        <v>22722</v>
       </c>
       <c r="H37" s="17" t="n">
-        <v>31848</v>
+        <v>22722</v>
       </c>
     </row>
     <row r="38">
@@ -5798,28 +4802,28 @@
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду32 Ру25</t>
+          <t>Захлопка фланцевая горизонтальная Ду50</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>522-01.239</t>
+          <t>529-03.011</t>
         </is>
       </c>
       <c r="D38" s="15" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38" s="15" t="n">
-        <v>5.6</v>
+        <v>11.2</v>
       </c>
       <c r="G38" s="17" t="n">
-        <v>10430</v>
+        <v>20860</v>
       </c>
       <c r="H38" s="17" t="n">
-        <v>31290</v>
+        <v>20860</v>
       </c>
     </row>
     <row r="39">
@@ -5828,28 +4832,28 @@
       </c>
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ20 Ру25</t>
+          <t>Кингстон донный фланцевый Ду32Ру2,5</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>УН521-3М.324</t>
+          <t>527-03.014</t>
         </is>
       </c>
       <c r="D39" s="15" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>5.3</v>
+        <v>11.2</v>
       </c>
       <c r="G39" s="17" t="n">
-        <v>9871</v>
+        <v>20860</v>
       </c>
       <c r="H39" s="17" t="n">
-        <v>29613</v>
+        <v>20860</v>
       </c>
     </row>
     <row r="40">
@@ -5858,28 +4862,28 @@
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25 Ру 40 без маховика , без крышки корпуса</t>
+          <t>Клапан фланцевый угловой Ду50</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>521-01.466</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D40" s="15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F40" s="15" t="n">
-        <v>3.1</v>
+        <v>11</v>
       </c>
       <c r="G40" s="17" t="n">
-        <v>5774</v>
+        <v>20488</v>
       </c>
       <c r="H40" s="17" t="n">
-        <v>28870</v>
+        <v>20488</v>
       </c>
     </row>
     <row r="41">
@@ -5888,28 +4892,28 @@
       </c>
       <c r="B41" s="18" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25 Ру 40</t>
+          <t>Клапан фланцевый угловой Ду50</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>521-3м.634</t>
+          <t>521-01.500</t>
         </is>
       </c>
       <c r="D41" s="15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>3.1</v>
+        <v>11</v>
       </c>
       <c r="G41" s="17" t="n">
-        <v>5774</v>
+        <v>20488</v>
       </c>
       <c r="H41" s="17" t="n">
-        <v>28870</v>
+        <v>20488</v>
       </c>
     </row>
     <row r="42">
@@ -5918,28 +4922,28 @@
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду70</t>
+          <t>Клапан фланц. пожарный проходной  Ду50</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>522-3м.575</t>
+          <t>595-01.002</t>
         </is>
       </c>
       <c r="D42" s="15" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E42" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="15" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="G42" s="17" t="n">
-        <v>28869</v>
+        <v>20488</v>
       </c>
       <c r="H42" s="17" t="n">
-        <v>28869</v>
+        <v>20488</v>
       </c>
     </row>
     <row r="43">
@@ -5948,28 +4952,28 @@
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>Кран трехходовой штуцерный Ду65 Ру10</t>
+          <t>Клапан фланцевый угловой Ду50</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>521-01.147</t>
         </is>
       </c>
       <c r="D43" s="15" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E43" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>15</v>
+        <v>10.8</v>
       </c>
       <c r="G43" s="17" t="n">
-        <v>27938</v>
+        <v>20115</v>
       </c>
       <c r="H43" s="17" t="n">
-        <v>27938</v>
+        <v>20115</v>
       </c>
     </row>
     <row r="44">
@@ -5978,28 +4982,28 @@
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан фланц. пожарный проходной  Ду50</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>521-3м.58</t>
+          <t>595-03.009</t>
         </is>
       </c>
       <c r="D44" s="15" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2.1</v>
+        <v>10.3</v>
       </c>
       <c r="G44" s="17" t="n">
-        <v>3911</v>
+        <v>19184</v>
       </c>
       <c r="H44" s="17" t="n">
-        <v>27377</v>
+        <v>19184</v>
       </c>
     </row>
     <row r="45">
@@ -6008,28 +5012,28 @@
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая горизонтальная Ду80</t>
+          <t>Клапан для колонки указательной Ду10 Ру16</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>529-03.071</t>
+          <t>598-03.022-06</t>
         </is>
       </c>
       <c r="D45" s="15" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14.4</v>
+        <v>1.5</v>
       </c>
       <c r="G45" s="17" t="n">
-        <v>26820</v>
+        <v>2794</v>
       </c>
       <c r="H45" s="17" t="n">
-        <v>26820</v>
+        <v>16764</v>
       </c>
     </row>
     <row r="46">
@@ -6038,28 +5042,28 @@
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>Клапан невозвратно -приемный Ду 65</t>
+          <t>Кран двухходовой фланцевый Ду 50 Ру6</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>522-35.4044-01</t>
+          <t>УН536-3М.74</t>
         </is>
       </c>
       <c r="D46" s="15" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E46" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="15" t="n">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G46" s="17" t="n">
-        <v>25144</v>
+        <v>16390</v>
       </c>
       <c r="H46" s="17" t="n">
-        <v>25144</v>
+        <v>16390</v>
       </c>
     </row>
     <row r="47">
@@ -6068,28 +5072,28 @@
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду25</t>
+          <t>Задвижка клинкетная Ду 50, без клиньев</t>
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>(541-03.232)</t>
+          <t>532-01.013</t>
         </is>
       </c>
       <c r="D47" s="15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>1.6</v>
+        <v>8.5</v>
       </c>
       <c r="G47" s="17" t="n">
-        <v>2980</v>
+        <v>15831</v>
       </c>
       <c r="H47" s="17" t="n">
-        <v>23840</v>
+        <v>15831</v>
       </c>
     </row>
     <row r="48">
@@ -6098,28 +5102,28 @@
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду60</t>
+          <t>Фильтр штуцрный Ду 20</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>532-01.014</t>
+          <t>427-03.128-2</t>
         </is>
       </c>
       <c r="D48" s="15" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E48" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="15" t="n">
-        <v>12.2</v>
+        <v>8.5</v>
       </c>
       <c r="G48" s="17" t="n">
-        <v>22722</v>
+        <v>15831</v>
       </c>
       <c r="H48" s="17" t="n">
-        <v>22722</v>
+        <v>15831</v>
       </c>
     </row>
     <row r="49">
@@ -6128,28 +5132,28 @@
       </c>
       <c r="B49" s="18" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая горизонтальная Ду50</t>
+          <t>кран штуцерный спускной Ду 15 Ру25</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>529-03.011</t>
+          <t>528-3м.73</t>
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>11.2</v>
+        <v>1.8</v>
       </c>
       <c r="G49" s="17" t="n">
-        <v>20860</v>
+        <v>3390</v>
       </c>
       <c r="H49" s="17" t="n">
-        <v>20860</v>
+        <v>13560</v>
       </c>
     </row>
     <row r="50">
@@ -6158,12 +5162,12 @@
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду32Ру2,5</t>
+          <t>Клапан предохранит. фланцевый угловой Ду32Ру4</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>527-03.014</t>
+          <t>524-03.090</t>
         </is>
       </c>
       <c r="D50" s="15" t="n">
@@ -6173,13 +5177,13 @@
         <v>1</v>
       </c>
       <c r="F50" s="15" t="n">
-        <v>11.2</v>
+        <v>7</v>
       </c>
       <c r="G50" s="17" t="n">
-        <v>20860</v>
+        <v>13038</v>
       </c>
       <c r="H50" s="17" t="n">
-        <v>20860</v>
+        <v>13038</v>
       </c>
     </row>
     <row r="51">
@@ -6188,28 +5192,28 @@
       </c>
       <c r="B51" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду50</t>
+          <t>Клапан фланцевый проходной ДУ20 Ру25</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>УН521-3М.516</t>
         </is>
       </c>
       <c r="D51" s="15" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E51" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="G51" s="17" t="n">
-        <v>20488</v>
+        <v>10244</v>
       </c>
       <c r="H51" s="17" t="n">
-        <v>20488</v>
+        <v>10244</v>
       </c>
     </row>
     <row r="52">
@@ -6218,28 +5222,28 @@
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду50</t>
+          <t>Кран двухходовой фланцевый Ду32 Ру6</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>521-01.500</t>
+          <t>УН536-3М.72</t>
         </is>
       </c>
       <c r="D52" s="15" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E52" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G52" s="17" t="n">
-        <v>20488</v>
+        <v>9312</v>
       </c>
       <c r="H52" s="17" t="n">
-        <v>20488</v>
+        <v>9312</v>
       </c>
     </row>
     <row r="53">
@@ -6248,28 +5252,28 @@
       </c>
       <c r="B53" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланц. пожарный проходной  Ду50</t>
+          <t>Клапан штуцерный угловой Ду15</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>595-01.002</t>
+          <t>521-3м.666</t>
         </is>
       </c>
       <c r="D53" s="15" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G53" s="17" t="n">
-        <v>20488</v>
+        <v>3725</v>
       </c>
       <c r="H53" s="17" t="n">
-        <v>20488</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="54">
@@ -6278,28 +5282,28 @@
       </c>
       <c r="B54" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланц. пожарный угловой Ду32 Ру16</t>
+          <t>Клапан штуцерный угловой Ду15  без маховика , без крышки корпуса</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>595-01-010</t>
+          <t>522-01.500-04</t>
         </is>
       </c>
       <c r="D54" s="15" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E54" s="15" t="n">
         <v>2</v>
       </c>
       <c r="F54" s="15" t="n">
-        <v>5.4</v>
+        <v>2</v>
       </c>
       <c r="G54" s="17" t="n">
-        <v>10058</v>
+        <v>3725</v>
       </c>
       <c r="H54" s="17" t="n">
-        <v>20116</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="55">
@@ -6308,28 +5312,28 @@
       </c>
       <c r="B55" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду50</t>
+          <t>Эжектор ВЭЖ 6,3</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
         <is>
-          <t>521-01.147</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D55" s="15" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="E55" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>10.8</v>
+        <v>4</v>
       </c>
       <c r="G55" s="17" t="n">
-        <v>20115</v>
+        <v>7450</v>
       </c>
       <c r="H55" s="17" t="n">
-        <v>20115</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="56">
@@ -6338,28 +5342,28 @@
       </c>
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланц. пожарный проходной  Ду50</t>
+          <t>Клапан невозвратный штуцерный проходной Ду 10</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>595-03.009</t>
+          <t>522-01.493</t>
         </is>
       </c>
       <c r="D56" s="15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E56" s="15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" s="15" t="n">
-        <v>10.3</v>
+        <v>1</v>
       </c>
       <c r="G56" s="17" t="n">
-        <v>19184</v>
+        <v>1862</v>
       </c>
       <c r="H56" s="17" t="n">
-        <v>19184</v>
+        <v>7448</v>
       </c>
     </row>
     <row r="57">
@@ -6368,28 +5372,28 @@
       </c>
       <c r="B57" s="18" t="inlineStr">
         <is>
-          <t>Клапан для колонки указательной Ду10 Ру16</t>
+          <t>Клапан штуцерный угловой Ду25 Ру 40</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr">
         <is>
-          <t>598-03.022-06</t>
+          <t>521-01.466</t>
         </is>
       </c>
       <c r="D57" s="15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F57" s="15" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="G57" s="17" t="n">
-        <v>2794</v>
+        <v>5774</v>
       </c>
       <c r="H57" s="17" t="n">
-        <v>16764</v>
+        <v>5774</v>
       </c>
     </row>
     <row r="58">
@@ -6398,28 +5402,28 @@
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>Кран двухходовой фланцевый Ду 50 Ру6</t>
+          <t>Клапан штуцерный угловой Ду15</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>УН536-3М.74</t>
+          <t>521-01.468-04</t>
         </is>
       </c>
       <c r="D58" s="15" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="E58" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F58" s="15" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="G58" s="17" t="n">
-        <v>16390</v>
+        <v>3725</v>
       </c>
       <c r="H58" s="17" t="n">
-        <v>16390</v>
+        <v>3725</v>
       </c>
     </row>
     <row r="59">
@@ -6428,28 +5432,28 @@
       </c>
       <c r="B59" s="18" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 50, без клиньев</t>
+          <t>Клапан штуцерный угловой Ду15</t>
         </is>
       </c>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>532-01.013</t>
+          <t>522-01.500-04</t>
         </is>
       </c>
       <c r="D59" s="15" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="E59" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F59" s="15" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="G59" s="17" t="n">
-        <v>15831</v>
+        <v>3725</v>
       </c>
       <c r="H59" s="17" t="n">
-        <v>15831</v>
+        <v>3725</v>
       </c>
     </row>
     <row r="60">
@@ -6458,28 +5462,28 @@
       </c>
       <c r="B60" s="18" t="inlineStr">
         <is>
-          <t>Фильтр штуцрный Ду 20</t>
+          <t>Клапан штуцерный угловой Ду15Ру40</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>427-03.128-2</t>
+          <t>521-01.465-02</t>
         </is>
       </c>
       <c r="D60" s="15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E60" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F60" s="15" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="G60" s="17" t="n">
-        <v>15831</v>
+        <v>3725</v>
       </c>
       <c r="H60" s="17" t="n">
-        <v>15831</v>
+        <v>3725</v>
       </c>
     </row>
     <row r="61">
@@ -6488,711 +5492,27 @@
       </c>
       <c r="B61" s="18" t="inlineStr">
         <is>
-          <t>кран штуцерный спускной Ду 15 Ру25</t>
+          <t>кран штуцерный Ду6 Ру25</t>
         </is>
       </c>
       <c r="C61" s="14" t="inlineStr">
         <is>
-          <t>528-3м.73</t>
+          <t>536-3м.330</t>
         </is>
       </c>
       <c r="D61" s="15" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="G61" s="17" t="n">
-        <v>3390</v>
+        <v>931</v>
       </c>
       <c r="H61" s="17" t="n">
-        <v>13560</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="15" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="18" t="inlineStr">
-        <is>
-          <t>Клапан Ду20/10</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="inlineStr">
-        <is>
-          <t>581-С673-3</t>
-        </is>
-      </c>
-      <c r="D62" s="15" t="inlineStr"/>
-      <c r="E62" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F62" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G62" s="17" t="n">
-        <v>4470</v>
-      </c>
-      <c r="H62" s="17" t="n">
-        <v>13410</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="15" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="18" t="inlineStr">
-        <is>
-          <t>Клапан предохранит. фланцевый угловой Ду32Ру4</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="inlineStr">
-        <is>
-          <t>524-03.090</t>
-        </is>
-      </c>
-      <c r="D63" s="15" t="n">
-        <v>32</v>
-      </c>
-      <c r="E63" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="G63" s="17" t="n">
-        <v>13038</v>
-      </c>
-      <c r="H63" s="17" t="n">
-        <v>13038</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="15" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="18" t="inlineStr">
-        <is>
-          <t>Кланан Рр18-2 45/25</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="inlineStr">
-        <is>
-          <t>2619802305</t>
-        </is>
-      </c>
-      <c r="D64" s="15" t="inlineStr"/>
-      <c r="E64" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="G64" s="17" t="n">
-        <v>12665</v>
-      </c>
-      <c r="H64" s="17" t="n">
-        <v>12665</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="15" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="18" t="inlineStr">
-        <is>
-          <t>клапан</t>
-        </is>
-      </c>
-      <c r="C65" s="14" t="inlineStr">
-        <is>
-          <t>552-03.023</t>
-        </is>
-      </c>
-      <c r="D65" s="15" t="inlineStr"/>
-      <c r="E65" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F65" s="15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G65" s="17" t="n">
-        <v>6332</v>
-      </c>
-      <c r="H65" s="17" t="n">
-        <v>12664</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="15" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="18" t="inlineStr">
-        <is>
-          <t>Клапан фланц.  пожарный угловой Ду32 Ру10</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="inlineStr">
-        <is>
-          <t>595-03-006</t>
-        </is>
-      </c>
-      <c r="D66" s="15" t="n">
-        <v>32</v>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G66" s="17" t="n">
-        <v>10802</v>
-      </c>
-      <c r="H66" s="17" t="n">
-        <v>10802</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="15" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="18" t="inlineStr">
-        <is>
-          <t>Клапан фланцевый проходной ДУ20 Ру25</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="inlineStr">
-        <is>
-          <t>УН521-3М.516</t>
-        </is>
-      </c>
-      <c r="D67" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="E67" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G67" s="17" t="n">
-        <v>10244</v>
-      </c>
-      <c r="H67" s="17" t="n">
-        <v>10244</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="15" t="n">
-        <v>64</v>
-      </c>
-      <c r="B68" s="18" t="inlineStr">
-        <is>
-          <t>Стакан переборочный Ду20Ру100</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="inlineStr">
-        <is>
-          <t>554-03.909-03</t>
-        </is>
-      </c>
-      <c r="D68" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F68" s="15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G68" s="17" t="n">
-        <v>3166</v>
-      </c>
-      <c r="H68" s="17" t="n">
-        <v>9498</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="15" t="n">
-        <v>65</v>
-      </c>
-      <c r="B69" s="18" t="inlineStr">
-        <is>
-          <t>Кран двухходовой фланцевый Ду32 Ру6</t>
-        </is>
-      </c>
-      <c r="C69" s="14" t="inlineStr">
-        <is>
-          <t>УН536-3М.72</t>
-        </is>
-      </c>
-      <c r="D69" s="15" t="n">
-        <v>32</v>
-      </c>
-      <c r="E69" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G69" s="17" t="n">
-        <v>9312</v>
-      </c>
-      <c r="H69" s="17" t="n">
-        <v>9312</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="15" t="n">
-        <v>66</v>
-      </c>
-      <c r="B70" s="18" t="inlineStr">
-        <is>
-          <t>Стакан переборочный Ду25Ру100</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>554-35.156</t>
-        </is>
-      </c>
-      <c r="D70" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="E70" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F70" s="15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G70" s="17" t="n">
-        <v>4656</v>
-      </c>
-      <c r="H70" s="17" t="n">
-        <v>9312</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="15" t="n">
-        <v>67</v>
-      </c>
-      <c r="B71" s="18" t="inlineStr">
-        <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду32</t>
-        </is>
-      </c>
-      <c r="C71" s="14" t="inlineStr">
-        <is>
-          <t>541-03.224</t>
-        </is>
-      </c>
-      <c r="D71" s="15" t="n">
-        <v>32</v>
-      </c>
-      <c r="E71" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F71" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G71" s="17" t="n">
-        <v>2794</v>
-      </c>
-      <c r="H71" s="17" t="n">
-        <v>8382</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="15" t="n">
-        <v>68</v>
-      </c>
-      <c r="B72" s="18" t="inlineStr">
-        <is>
-          <t>Клапан штуцерный угловой Ду15</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>521-3м.666</t>
-        </is>
-      </c>
-      <c r="D72" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F72" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G72" s="17" t="n">
-        <v>3725</v>
-      </c>
-      <c r="H72" s="17" t="n">
-        <v>7450</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="15" t="n">
-        <v>69</v>
-      </c>
-      <c r="B73" s="18" t="inlineStr">
-        <is>
-          <t>Клапан штуцерный угловой Ду15  без маховика , без крышки корпуса</t>
-        </is>
-      </c>
-      <c r="C73" s="14" t="inlineStr">
-        <is>
-          <t>522-01.500-04</t>
-        </is>
-      </c>
-      <c r="D73" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="E73" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F73" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G73" s="17" t="n">
-        <v>3725</v>
-      </c>
-      <c r="H73" s="17" t="n">
-        <v>7450</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="15" t="n">
-        <v>70</v>
-      </c>
-      <c r="B74" s="18" t="inlineStr">
-        <is>
-          <t>Эжектор ВЭЖ 6,3</t>
-        </is>
-      </c>
-      <c r="C74" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="E74" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G74" s="17" t="n">
-        <v>7450</v>
-      </c>
-      <c r="H74" s="17" t="n">
-        <v>7450</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="15" t="n">
-        <v>71</v>
-      </c>
-      <c r="B75" s="18" t="inlineStr">
-        <is>
-          <t>Клапан невозвратный штуцерный проходной Ду 10</t>
-        </is>
-      </c>
-      <c r="C75" s="14" t="inlineStr">
-        <is>
-          <t>522-01.493</t>
-        </is>
-      </c>
-      <c r="D75" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E75" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F75" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="17" t="n">
-        <v>1862</v>
-      </c>
-      <c r="H75" s="17" t="n">
-        <v>7448</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="15" t="n">
-        <v>72</v>
-      </c>
-      <c r="B76" s="18" t="inlineStr">
-        <is>
-          <t>Клапан штуцерный угловой Ду25 Ру 40</t>
-        </is>
-      </c>
-      <c r="C76" s="14" t="inlineStr">
-        <is>
-          <t>521-01.466</t>
-        </is>
-      </c>
-      <c r="D76" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="E76" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G76" s="17" t="n">
-        <v>5774</v>
-      </c>
-      <c r="H76" s="17" t="n">
-        <v>5774</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="15" t="n">
-        <v>73</v>
-      </c>
-      <c r="B77" s="18" t="inlineStr">
-        <is>
-          <t>Стакан переборочный Ду10Ру100</t>
-        </is>
-      </c>
-      <c r="C77" s="14" t="inlineStr">
-        <is>
-          <t>554-35.265</t>
-        </is>
-      </c>
-      <c r="D77" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E77" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="F77" s="15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G77" s="17" t="n">
-        <v>1118</v>
-      </c>
-      <c r="H77" s="17" t="n">
-        <v>5590</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="15" t="n">
-        <v>74</v>
-      </c>
-      <c r="B78" s="18" t="inlineStr">
-        <is>
-          <t>Клапан штуцерный угловой Ду15</t>
-        </is>
-      </c>
-      <c r="C78" s="14" t="inlineStr">
-        <is>
-          <t>521-01.468-04</t>
-        </is>
-      </c>
-      <c r="D78" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G78" s="17" t="n">
-        <v>3725</v>
-      </c>
-      <c r="H78" s="17" t="n">
-        <v>3725</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="15" t="n">
-        <v>75</v>
-      </c>
-      <c r="B79" s="18" t="inlineStr">
-        <is>
-          <t>Клапан штуцерный угловой Ду15</t>
-        </is>
-      </c>
-      <c r="C79" s="14" t="inlineStr">
-        <is>
-          <t>521-01.468-08</t>
-        </is>
-      </c>
-      <c r="D79" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="E79" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G79" s="17" t="n">
-        <v>3725</v>
-      </c>
-      <c r="H79" s="17" t="n">
-        <v>3725</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="15" t="n">
-        <v>76</v>
-      </c>
-      <c r="B80" s="18" t="inlineStr">
-        <is>
-          <t>Клапан штуцерный угловой Ду15</t>
-        </is>
-      </c>
-      <c r="C80" s="14" t="inlineStr">
-        <is>
-          <t>522-01.500-04</t>
-        </is>
-      </c>
-      <c r="D80" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G80" s="17" t="n">
-        <v>3725</v>
-      </c>
-      <c r="H80" s="17" t="n">
-        <v>3725</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="15" t="n">
-        <v>77</v>
-      </c>
-      <c r="B81" s="18" t="inlineStr">
-        <is>
-          <t>Клапан штуцерный угловой Ду15Ру40</t>
-        </is>
-      </c>
-      <c r="C81" s="14" t="inlineStr">
-        <is>
-          <t>521-01.465-02</t>
-        </is>
-      </c>
-      <c r="D81" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G81" s="17" t="n">
-        <v>3725</v>
-      </c>
-      <c r="H81" s="17" t="n">
-        <v>3725</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="15" t="n">
-        <v>78</v>
-      </c>
-      <c r="B82" s="18" t="inlineStr">
-        <is>
-          <t>Клапан невозвратный штуцерный проходной Ду20 Ру40</t>
-        </is>
-      </c>
-      <c r="C82" s="14" t="inlineStr">
-        <is>
-          <t>522-3м-9</t>
-        </is>
-      </c>
-      <c r="D82" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="E82" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F82" s="15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G82" s="17" t="n">
-        <v>3539</v>
-      </c>
-      <c r="H82" s="17" t="n">
-        <v>3539</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="15" t="n">
-        <v>79</v>
-      </c>
-      <c r="B83" s="18" t="inlineStr">
-        <is>
-          <t>Клапан предохранительный штуцерный угловой Ду10 ру 6,5-9</t>
-        </is>
-      </c>
-      <c r="C83" s="14" t="inlineStr">
-        <is>
-          <t>524-03.004</t>
-        </is>
-      </c>
-      <c r="D83" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E83" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G83" s="17" t="n">
-        <v>2831</v>
-      </c>
-      <c r="H83" s="17" t="n">
-        <v>2831</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="15" t="n">
-        <v>80</v>
-      </c>
-      <c r="B84" s="18" t="inlineStr">
-        <is>
-          <t>кран штуцерный Ду6 Ру25</t>
-        </is>
-      </c>
-      <c r="C84" s="14" t="inlineStr">
-        <is>
-          <t>536-3м.330</t>
-        </is>
-      </c>
-      <c r="D84" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="E84" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F84" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G84" s="17" t="n">
-        <v>931</v>
-      </c>
-      <c r="H84" s="17" t="n">
         <v>1862</v>
       </c>
     </row>

--- a/outputs/marine_equipment/Изменение_цен_по_ставке.xlsx
+++ b/outputs/marine_equipment/Изменение_цен_по_ставке.xlsx
@@ -722,13 +722,13 @@
         <v>57</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>3018</v>
+        <v>3002</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>5621366</v>
+        <v>5591565</v>
       </c>
       <c r="F9" s="18" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32</t>
+          <t>Клапан штуцерный угловой Ду32,без маховика , без крышки корпуса</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
@@ -3760,7 +3760,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>57 позиций  206 шт  3 018 кг на 5 621 366 руб. В договоре их не было совсем или стояло «по согласованию» — сравнивать не с чем  это новая цена  а не изменение.</t>
+          <t>57 позиций  207 шт  3 002 кг на 5 591 565 руб. В договоре их не было совсем или стояло «по согласованию» — сравнивать не с чем  это новая цена  а не изменение.</t>
         </is>
       </c>
     </row>
@@ -4202,28 +4202,28 @@
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 125</t>
+          <t>Клапан фланцевый угловой Ду100</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>532-01.018</t>
+          <t>522-35.4206</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E18" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>37.2</v>
+        <v>35.4</v>
       </c>
       <c r="G18" s="17" t="n">
-        <v>69285</v>
+        <v>65932</v>
       </c>
       <c r="H18" s="17" t="n">
-        <v>69285</v>
+        <v>65932</v>
       </c>
     </row>
     <row r="19">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду100</t>
+          <t>Захлопка фланцевая вертикальная Ду100</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>522-35.4206</t>
+          <t>529-03.003</t>
         </is>
       </c>
       <c r="D19" s="15" t="n">
@@ -4247,13 +4247,13 @@
         <v>1</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>35.4</v>
+        <v>33.7</v>
       </c>
       <c r="G19" s="17" t="n">
-        <v>65932</v>
+        <v>62766</v>
       </c>
       <c r="H19" s="17" t="n">
-        <v>65932</v>
+        <v>62766</v>
       </c>
     </row>
     <row r="20">
@@ -4262,12 +4262,12 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая вертикальная Ду100</t>
+          <t>Клапан фланцевый проходной Ду100</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>529-03.003</t>
+          <t>521-3М.511</t>
         </is>
       </c>
       <c r="D20" s="15" t="n">
@@ -4277,13 +4277,13 @@
         <v>1</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>33.7</v>
+        <v>29</v>
       </c>
       <c r="G20" s="17" t="n">
-        <v>62766</v>
+        <v>54012</v>
       </c>
       <c r="H20" s="17" t="n">
-        <v>62766</v>
+        <v>54012</v>
       </c>
     </row>
     <row r="21">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду100</t>
+          <t>Задвижка клинкетная Ду 100</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>521-3М.511</t>
+          <t>532-01.017</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
@@ -4307,13 +4307,13 @@
         <v>1</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>29</v>
+        <v>28.3</v>
       </c>
       <c r="G21" s="17" t="n">
-        <v>54012</v>
+        <v>52709</v>
       </c>
       <c r="H21" s="17" t="n">
-        <v>54012</v>
+        <v>52709</v>
       </c>
     </row>
     <row r="22">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 100</t>
+          <t>Клапан фланцевый угловой Ду100</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>532-01.017</t>
+          <t>522-35.4171-02</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
@@ -4337,13 +4337,13 @@
         <v>1</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>28.3</v>
+        <v>28</v>
       </c>
       <c r="G22" s="17" t="n">
-        <v>52709</v>
+        <v>52150</v>
       </c>
       <c r="H22" s="17" t="n">
-        <v>52709</v>
+        <v>52150</v>
       </c>
     </row>
     <row r="23">
@@ -4352,28 +4352,28 @@
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду100</t>
+          <t>Фильтр штуцрный Ду 25</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>522-35.4171-02</t>
+          <t>427-03.129-1</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>28</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>52150</v>
+        <v>17135</v>
       </c>
       <c r="H23" s="17" t="n">
-        <v>52150</v>
+        <v>51405</v>
       </c>
     </row>
     <row r="24">
@@ -4382,28 +4382,28 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>Фильтр штуцрный Ду 25</t>
+          <t>Захлопка фланцевая угловая Ду100</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>427-03.129-1</t>
+          <t>529-35-1405</t>
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>9.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="G24" s="17" t="n">
-        <v>17135</v>
+        <v>48425</v>
       </c>
       <c r="H24" s="17" t="n">
-        <v>51405</v>
+        <v>48425</v>
       </c>
     </row>
     <row r="25">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>529-35-1405</t>
+          <t>529-03.073</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
@@ -4427,13 +4427,13 @@
         <v>1</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>26</v>
+        <v>24.7</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>48425</v>
+        <v>46004</v>
       </c>
       <c r="H25" s="17" t="n">
-        <v>48425</v>
+        <v>46004</v>
       </c>
     </row>
     <row r="26">
@@ -4442,28 +4442,28 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая угловая Ду100</t>
+          <t>грибок ду 200</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>529-03.073</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>24.7</v>
+        <v>10.6</v>
       </c>
       <c r="G26" s="17" t="n">
-        <v>46004</v>
+        <v>19742</v>
       </c>
       <c r="H26" s="17" t="n">
-        <v>46004</v>
+        <v>39484</v>
       </c>
     </row>
     <row r="27">
